--- a/data/trans_orig/IQ2601_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ2601_R2-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>74495</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>64808</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>84436</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>43,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,12%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>80567</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>71689</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>89957</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>71243</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>90789</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>60,12%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>53,49%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>74495</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>64369</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>84298</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>50,39%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141301</t>
+          <t>142267</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168964</t>
+          <t>168279</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>73328</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>63387</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>83015</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>42,88%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>56,16%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>53445</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>44055</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>62323</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>43223</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>62769</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,88%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,51%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>73328</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>63525</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>83454</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>49,61%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112871</t>
+          <t>113556</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140534</t>
+          <t>139568</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,52%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>147823</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>147823</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>147823</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>134012</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>134012</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>134012</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>147823</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>147823</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>147823</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>135101</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>122846</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>145237</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>64,46%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>58,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>69,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>122450</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>113069</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>132545</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>111092</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>132105</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>63,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>58,68%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>68,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>135101</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>123180</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>145292</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>64,46%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>241213</t>
+          <t>243005</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>272783</t>
+          <t>272575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,76%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74500</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>64364</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>86755</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>35,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>30,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>41,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>70237</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>60142</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>79618</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>60582</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>81595</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>36,45%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>41,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>74500</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>64309</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>86421</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>35,54%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>129505</t>
+          <t>129713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>161075</t>
+          <t>159283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>209601</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>209601</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>209601</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>308</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>192687</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>192687</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>192687</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>209601</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>209601</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>209601</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>112539</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>103872</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>119667</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>78,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>72,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>83,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>103636</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>96117</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>110263</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>95929</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>110568</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>78,74%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>73,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>112539</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>102657</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>119218</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>78,49%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>204632</t>
+          <t>206027</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>226366</t>
+          <t>227378</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30838</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23710</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>39505</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>21,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>27,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>27979</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>21352</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>35498</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>21047</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>35686</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>21,26%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>26,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>30838</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>24159</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>40720</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>21,51%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48626</t>
+          <t>47614</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70360</t>
+          <t>68965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>143377</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>143377</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>143377</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>131615</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>131615</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>131615</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>143377</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>143377</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>143377</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>140338</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>129569</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>150646</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>67,97%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>62,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>72,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>144384</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>132403</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>155655</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>133520</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>154594</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>69,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>64,16%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>75,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>140338</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>129128</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>150437</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>67,97%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>268676</t>
+          <t>268092</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>300872</t>
+          <t>299279</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,5%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>66129</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>55821</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>76898</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>32,03%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>27,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>37,24%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>61965</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>50694</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>73946</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>51755</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>72829</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>30,03%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>24,57%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>35,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>66129</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>56030</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>77339</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>32,03%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111944</t>
+          <t>113537</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>144140</t>
+          <t>144724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206467</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206467</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206467</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206349</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206349</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206349</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206467</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206467</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206467</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>462474</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>440089</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>481463</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>65,39%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>62,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>674</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>451037</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>432164</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>469291</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>433101</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>470992</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>67,86%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>70,61%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>462474</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>439742</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>480392</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>65,39%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>887289</t>
+          <t>885396</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>940472</t>
+          <t>942134</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>244794</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>225805</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>267179</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>34,61%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,93%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>318</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>213626</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>195372</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>232499</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>193671</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>231562</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>32,14%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>29,39%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34,98%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>244794</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>226876</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>267526</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>34,61%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>431458</t>
+          <t>429796</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>484641</t>
+          <t>486534</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>707268</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>707268</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>707268</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>992</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>707268</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>707268</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>707268</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>70765</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>59912</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>81186</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40,48%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>54,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>65252</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>54989</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>74403</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>55517</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>75453</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>47,29%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>70765</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>60753</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>80761</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>47,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119647</t>
+          <t>121674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150822</t>
+          <t>150066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>77243</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>66822</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>88096</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>52,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>45,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>59,52%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>72743</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>63592</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>83006</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>62542</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>82478</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>52,71%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>46,08%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>60,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>77243</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>67247</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>87255</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>52,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>135182</t>
+          <t>135938</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166357</t>
+          <t>164330</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,46%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148008</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148008</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148008</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>137995</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>137995</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>137995</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148008</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148008</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>108092</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>96077</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>120319</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>49,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>44,13%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>55,26%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>107335</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>94497</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>117632</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>94440</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>118533</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>54,23%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>47,74%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>59,43%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>108092</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>96620</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>120971</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>49,65%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>198149</t>
+          <t>199555</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>232215</t>
+          <t>230656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>109638</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>97411</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>121653</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>50,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>44,74%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>55,87%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>90593</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>80296</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>103431</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>79395</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>103488</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>45,77%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>40,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>52,26%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>109638</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>96759</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>121110</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>50,35%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183443</t>
+          <t>185002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>217509</t>
+          <t>216103</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>217730</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>217730</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>217730</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>197928</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>197928</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>197928</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>217730</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>217730</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>217730</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>84377</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>74076</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>94441</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>53,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>46,76%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>59,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>80943</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>70563</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>90490</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>69819</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>89840</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>54,03%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>60,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>84377</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>74077</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>94972</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>53,27%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>151527</t>
+          <t>150987</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>179091</t>
+          <t>178792</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74030</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>63966</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>84331</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>46,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>40,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>53,24%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>59325</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>79252</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>59975</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>79996</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>45,97%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>39,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>52,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>74030</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>63435</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>84330</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>46,73%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129132</t>
+          <t>129431</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>156696</t>
+          <t>157236</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,01%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158407</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158407</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158407</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>149815</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>149815</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>149815</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158407</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158407</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158407</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>92980</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>80404</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>105630</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>46,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>39,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>52,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>107577</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>95560</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>120616</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>95992</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>119199</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>53,24%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>47,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>59,7%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>92980</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>79811</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>105339</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>46,04%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>185250</t>
+          <t>183902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217855</t>
+          <t>218528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>108967</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>96317</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>121543</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>53,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>60,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>94467</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>81428</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>106484</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>82845</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>106052</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>46,76%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>40,3%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>52,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>108967</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>96608</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>122136</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>53,96%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>186136</t>
+          <t>185463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>218741</t>
+          <t>220089</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,48%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201947</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201947</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201947</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>202044</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>202044</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>202044</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>201947</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>201947</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>201947</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>356214</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>332768</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>378199</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>49,06%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>45,83%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>52,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>361108</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>337344</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>381526</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>340065</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>382882</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>52,5%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>49,05%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>55,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>356214</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>331716</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>378087</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>49,06%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>687891</t>
+          <t>687930</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>749600</t>
+          <t>751363</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>369878</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>347893</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>393324</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>50,94%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>47,91%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>54,17%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>326675</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>306257</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>350439</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>304901</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>347718</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>47,5%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>44,53%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>50,95%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>369878</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>348005</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>394376</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>50,94%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>664275</t>
+          <t>662512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>725984</t>
+          <t>725945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,34%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>726092</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>726092</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>726092</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>990</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>687783</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>687783</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>687783</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1035</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>726092</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>726092</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>726092</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>95303</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>84592</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>104648</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>64,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>71,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>80417</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>71054</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>90045</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>70559</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>89828</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>61,31%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>54,17%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>68,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>95303</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>85574</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>105285</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>64,69%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>161432</t>
+          <t>160676</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>189632</t>
+          <t>189172</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52011</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>42666</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>62722</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>50744</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41116</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>60107</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41333</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>60602</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,69%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>45,83%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>52011</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>42029</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61740</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>35,31%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88842</t>
+          <t>89302</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117042</t>
+          <t>117798</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131161</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131161</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131161</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>147314</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>147314</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>147314</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>150131</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>138245</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>160839</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>67,69%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>62,33%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>72,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>141649</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>131097</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>152239</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>131110</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>151029</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>69,17%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>64,02%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>74,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>150131</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>138914</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>160736</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>67,69%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>62,63%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>277094</t>
+          <t>275236</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>307974</t>
+          <t>305676</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>71,66%</t>
         </is>
       </c>
     </row>
@@ -5073,74 +5073,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>71659</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60951</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>83545</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32,31%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>37,67%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>63140</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>52550</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>73692</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>53760</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>73679</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>30,83%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>26,25%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>35,98%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>71659</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>61054</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>82876</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>32,31%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>27,53%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>37,37%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>207</t>
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>118605</t>
+          <t>120903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149485</t>
+          <t>151343</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221790</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221790</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221790</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>204789</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>204789</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>204789</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221790</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221790</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221790</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>108309</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>98123</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>117499</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>65,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>59,29%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>70,99%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>91812</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>82423</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>101553</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>82525</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>100847</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>60,03%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>53,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>66,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>108309</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>97787</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>117445</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>65,44%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186055</t>
+          <t>185388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215254</t>
+          <t>213550</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,06%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57198</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>48008</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>67384</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,01%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,71%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61132</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>51391</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>70521</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>52097</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>70419</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>39,97%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>57198</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>48062</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>67720</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>34,56%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103197</t>
+          <t>104901</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132396</t>
+          <t>133063</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165507</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165507</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165507</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>152944</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>152944</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>152944</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165507</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165507</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165507</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>120605</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>107949</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>131916</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>59,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>53,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>65,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>130388</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>118387</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>141883</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>119352</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>142412</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>63,71%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>57,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>69,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>120605</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>109354</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>132527</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>59,49%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>234498</t>
+          <t>233594</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>268105</t>
+          <t>266696</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,47%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82116</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>70805</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>94772</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>40,51%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>34,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>46,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74258</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>62763</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>86259</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>62234</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>85294</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>36,29%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>30,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>42,15%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>82116</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>70194</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>93367</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>40,51%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>139262</t>
+          <t>140671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>172869</t>
+          <t>173773</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202721</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202721</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202721</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>204646</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>204646</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>204646</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202721</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202721</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202721</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>474348</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>451187</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>497019</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>64,33%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,41%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>669</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>444266</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>424179</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>463217</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>422565</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>463696</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>64,06%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>61,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>66,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>474348</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>453926</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>495865</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>64,33%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>887063</t>
+          <t>890646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>948036</t>
+          <t>946107</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,12%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>262984</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>240313</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>286145</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>35,67%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,59%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>374</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>249274</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>230323</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>269361</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>229844</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>270975</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,94%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,21%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>262984</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>241467</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>283406</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>35,67%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>482835</t>
+          <t>484764</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>543808</t>
+          <t>540225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1043</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22268</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17689</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26899</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>68,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>54,47%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>82,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>21242</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17858</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24327</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>21666</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17765</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>24246</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>78,11%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>65,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>23684</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>18197</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>28280</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>67,22%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>44926</t>
+          <t>43933</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39345</t>
+          <t>38003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50704</t>
+          <t>48783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5573</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14783</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17,16%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,53%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5953</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2868</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9337</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6070</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3490</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9971</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>21,89%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,54%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11549</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6953</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17036</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>32,78%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>17502</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23083</t>
+          <t>22205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>27195</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>27195</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>27195</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>47313</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>40970</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>52010</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>80,48%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>69,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>88,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>26352</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20891</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>31083</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>67,03%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>53,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>79,06%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50655</t>
+          <t>25902</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43928</t>
+          <t>20529</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55636</t>
+          <t>30816</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>77007</t>
+          <t>73216</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67998</t>
+          <t>64272</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84087</t>
+          <t>80389</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11479</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6782</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17822</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>19,52%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11,54%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>30,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12962</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8231</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18423</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>32,97%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>46,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>8548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>18835</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>24827</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17747</t>
+          <t>17767</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33836</t>
+          <t>33884</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>98156</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>98156</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>98156</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26694</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20038</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31659</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>64,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,28%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>76,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>22701</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18322</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26145</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>76,17%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>61,47%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>87,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28196</t>
+          <t>19678</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21966</t>
+          <t>15455</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33474</t>
+          <t>23359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>50897</t>
+          <t>46371</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57911</t>
+          <t>52794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,16%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14813</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9848</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21469</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>23,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,72%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7104</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3660</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11483</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>23,83%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>38,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15992</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22222</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>23096</t>
+          <t>22054</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>15631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31550</t>
+          <t>28621</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>29805</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>29805</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>29805</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>73993</t>
+          <t>68425</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73993</t>
+          <t>68425</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73993</t>
+          <t>68425</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34603</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28351</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>38976</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>75,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>62,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>85,49%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>28689</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22960</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34312</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>62,72%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>50,2%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>75,01%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>37714</t>
+          <t>27060</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32036</t>
+          <t>21357</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42872</t>
+          <t>32102</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>66403</t>
+          <t>61663</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57883</t>
+          <t>52892</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73777</t>
+          <t>68995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10991</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6618</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17243</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14,51%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>37,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>17052</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11429</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22781</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>37,28%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>24,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>49,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>17479</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17793</t>
+          <t>23182</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>29167</t>
+          <t>28470</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21793</t>
+          <t>21138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37687</t>
+          <t>37241</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>45594</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>45594</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>45594</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>45741</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>45741</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>45741</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>44539</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>44539</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>44539</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>95570</t>
+          <t>90133</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>95570</t>
+          <t>90133</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>95570</t>
+          <t>90133</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>130878</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>119578</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>140854</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>67,04%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>78,97%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>98984</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>89370</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>107503</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>69,68%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>62,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>75,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>140248</t>
+          <t>94305</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128483</t>
+          <t>85022</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>152196</t>
+          <t>103047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>239232</t>
+          <t>225183</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>223897</t>
+          <t>211054</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>252531</t>
+          <t>238878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>47487</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>37511</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>58787</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,62%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,03%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>32,96%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>43071</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>34552</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>52685</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>30,32%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>24,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,09%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51522</t>
+          <t>44252</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39574</t>
+          <t>35510</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63287</t>
+          <t>53535</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>94592</t>
+          <t>91739</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81293</t>
+          <t>78044</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>109927</t>
+          <t>105868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>142055</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>142055</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>142055</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138557</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138557</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138557</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>333824</t>
+          <t>316922</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>333824</t>
+          <t>316922</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>333824</t>
+          <t>316922</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
